--- a/Exc2/FURPS_list.xlsx
+++ b/Exc2/FURPS_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
   <si>
     <t>Код</t>
   </si>
@@ -39,69 +39,42 @@
     <t>F1</t>
   </si>
   <si>
-    <t>Пользователи сайта и интернет-банка видят актуальный список доступных депозитов</t>
-  </si>
-  <si>
     <t>Клиенты должны иметь возможность в любой момент времени видеть актуальные данные по депозитам как на сайте, так и в интеренет-банке</t>
   </si>
   <si>
     <t>F2</t>
   </si>
   <si>
-    <t>Централизованный расчет и ведение списка депозитов</t>
-  </si>
-  <si>
     <t>Все сотрудники, имеющие доступ в АБС, могут видеть актуальные данные по ставкам. Данные на сайте обновляются оттуда же</t>
   </si>
   <si>
     <t>F3</t>
   </si>
   <si>
-    <t>Пользователи интернет-банка видят персонализированные предложения по депозитам</t>
-  </si>
-  <si>
     <t>F4</t>
   </si>
   <si>
-    <t>Возможность для клиента оставить заявку на сайте на размещение депозита</t>
-  </si>
-  <si>
     <t>Клиент может оставить завку на депозит из списка, указав контактные данные</t>
   </si>
   <si>
     <t>F5</t>
   </si>
   <si>
-    <t>Заявка, размещенная на сайте попадает в ПО call-центра</t>
-  </si>
-  <si>
     <t>F6</t>
   </si>
   <si>
-    <t>Пользователь интернет-банка может выбрать заинтересовавший депозит из списка</t>
-  </si>
-  <si>
     <t>Клиент интерент-банка может кликом выбрать понравившийся депозит и через форму отправить заявку в банк</t>
   </si>
   <si>
     <t>F7</t>
   </si>
   <si>
-    <t>Заявка на депозит, оформленная в интернет-банке, попадает в АБС</t>
-  </si>
-  <si>
     <t>F8</t>
   </si>
   <si>
-    <t>Оператор front-офиса может напрямую завести заявку от клиента при обращении в отделение</t>
-  </si>
-  <si>
     <t>F9</t>
   </si>
   <si>
-    <t>Все подтверждения операций, как размещение депозита подтверждаются СМС</t>
-  </si>
-  <si>
     <t>U</t>
   </si>
   <si>
@@ -111,9 +84,6 @@
     <t>U1</t>
   </si>
   <si>
-    <t>Единая стилистика всех пользовательских интерфейсов</t>
-  </si>
-  <si>
     <t>Общий гайдлайн/руководство по стилю</t>
   </si>
   <si>
@@ -132,30 +102,18 @@
     <t>R1</t>
   </si>
   <si>
-    <t>Высокая доступность (99,9%)</t>
-  </si>
-  <si>
     <t>R2</t>
   </si>
   <si>
-    <t>Безопасность данных</t>
-  </si>
-  <si>
     <t>Шифрование траффика</t>
   </si>
   <si>
     <t>R3</t>
   </si>
   <si>
-    <t>Резервное копирование</t>
-  </si>
-  <si>
     <t>R4</t>
   </si>
   <si>
-    <t>Масштабируемость</t>
-  </si>
-  <si>
     <t>Необходимо предусмотреть горизонтальное масштабирование систем</t>
   </si>
   <si>
@@ -174,12 +132,6 @@
     <t>P2</t>
   </si>
   <si>
-    <t>Кэширование</t>
-  </si>
-  <si>
-    <t>Может помочь ускорить обработку данных и запросов</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -189,46 +141,19 @@
     <t>S1</t>
   </si>
   <si>
-    <t>Документация</t>
-  </si>
-  <si>
-    <t>Необходима проработка документации, в том числе для дальнейшего расширения системы</t>
-  </si>
-  <si>
     <t>S2</t>
   </si>
   <si>
-    <t>Совместимость технологий</t>
-  </si>
-  <si>
     <t>+R</t>
   </si>
   <si>
     <t>+ Ограничения (Restricitions)</t>
   </si>
   <si>
-    <t>АБС поддерживает только вертикальное масштабирование</t>
-  </si>
-  <si>
-    <t>Лучше избежать прямой работы с API АБС</t>
-  </si>
-  <si>
-    <t>Технологический стек ограничен Java, .NET</t>
-  </si>
-  <si>
-    <t>Для очереди сообщений может быть использована только Kafka</t>
-  </si>
-  <si>
     <t>В интернет-банке клиент должен видеть как общие, так и персонализированные ставки.</t>
   </si>
   <si>
     <t>F10</t>
-  </si>
-  <si>
-    <t>Заявка на депозит, оформленная в front-офиса , попадает в АБС</t>
-  </si>
-  <si>
-    <t>Простой и интуитивно понятный интерфейс (friendly interface)</t>
   </si>
   <si>
     <t>Интерфейс должен быть интуитивно понятным и согласован с системой дизайна компании.</t>
@@ -241,33 +166,21 @@
 </t>
   </si>
   <si>
-    <t>Распределённость систем по нескольким зонам доступности</t>
-  </si>
-  <si>
     <t>Необходимо распределить системы по нескольким зонам доступности</t>
   </si>
   <si>
     <t>Наличие механизма переключения на резервный ЦОД.</t>
   </si>
   <si>
-    <t>Отклики и загрузка данных должны занимать миллисекунды.</t>
-  </si>
-  <si>
     <t>Скорость загрузки данных (интеграции)</t>
   </si>
   <si>
     <t>Совместимость необходима как из-за имеющихся тех. ограничений, так и из-за внутренней экспертизы (с учетом требований импортазамещения)</t>
   </si>
   <si>
-    <t>Требования импортазамещения</t>
-  </si>
-  <si>
     <t>Ограничения могут внести корректеровки в стек технологий.</t>
   </si>
   <si>
-    <t>Хранение перс. Данных, коммерческой тайны</t>
-  </si>
-  <si>
     <t>Более жесткие требования по шифрованию и хранению данных</t>
   </si>
   <si>
@@ -277,10 +190,97 @@
     <t>Под большим вопросом.</t>
   </si>
   <si>
-    <t>Попытаться макимально переиспользовать имеющихся технологий (MS SQL и Oracle)</t>
-  </si>
-  <si>
     <t>Опыт имеющеся команды</t>
+  </si>
+  <si>
+    <t>Должен вестить централизованный расчет и ведение списка депозитов</t>
+  </si>
+  <si>
+    <t>Пользователи сайта и интернет-банка должны видеть актуальный список доступных им депозитов</t>
+  </si>
+  <si>
+    <t>Интернет-банк должен предоставлять список персонализированных предложений по депозитам</t>
+  </si>
+  <si>
+    <t>На сайте должна быть предоставлена возможность клиенту оставить заявку на  размещение депозита</t>
+  </si>
+  <si>
+    <t>Заявка, размещенная пользователем на сайте должна автоматически попасть в ПО call-центра</t>
+  </si>
+  <si>
+    <t>Заявка на депозит, оформленная в интернет-банке, должна автоматически попасть в АБС</t>
+  </si>
+  <si>
+    <t>Пользователь интернет-банка должен иметь возможность выбрать заинтересовавший депозит из списка стандартных или персонализированных предложений</t>
+  </si>
+  <si>
+    <t>Оператор front-офиса должен иметь возможность напрямую завести заявку от клиента при обращении в отделение</t>
+  </si>
+  <si>
+    <t>Заявка на депозит, оформленная в front-офисе, должна попасть в АБС</t>
+  </si>
+  <si>
+    <t>Все подтверждения операций, такие как размещение депозита должны подтверждаться СМС</t>
+  </si>
+  <si>
+    <t>Все пользовательские интерфейсы должны бытиь реализованы в единая стилистике</t>
+  </si>
+  <si>
+    <t>Интерфейс дожен быть интуитивно понятным (friendly interface)</t>
+  </si>
+  <si>
+    <t>Потенциальная доступность  системы должна составлять (99,9%)</t>
+  </si>
+  <si>
+    <t>Должны быть реализованы требования к безопасности данных</t>
+  </si>
+  <si>
+    <t>Должно быть организовано резервное копирование</t>
+  </si>
+  <si>
+    <t>Приложение должно иметь возможность масштабироваться</t>
+  </si>
+  <si>
+    <t>Система должна иметь распределённость по нескольким зонам доступности</t>
+  </si>
+  <si>
+    <t>Отклики и загрузка данных должны занимать миллисекунды. Критерии качества в ТЗ.</t>
+  </si>
+  <si>
+    <t>Критерии качества в ТЗ.</t>
+  </si>
+  <si>
+    <t>Система должна иметь возможность кэшировать данные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Серверное кеширование. Кеширование агрегированных данных для дальнейших расчетов системы. </t>
+  </si>
+  <si>
+    <t>Должна быть создана и согласована проектная документация</t>
+  </si>
+  <si>
+    <t>Необходима проработка документации, в том числе для дальнейшего расширения системы (тех.задание, инструкции администратора и пользователя, методика проведения испытаний, методика опытно промышленной эксплуатации и т.п.)</t>
+  </si>
+  <si>
+    <t>Технологичесикий стек должен учитывать совместимость с технологиями, используемыми а Банке.</t>
+  </si>
+  <si>
+    <t>Должны быть учтены требования импортазамещения</t>
+  </si>
+  <si>
+    <t>Имеющиеся технологии (MS SQL и Oracle) должны быть максимально переиспользованы</t>
+  </si>
+  <si>
+    <t>Необходимо избежать прямой работы с API АБС</t>
+  </si>
+  <si>
+    <t>Система должна быть разработана с учетом требований хранения перс. Данных и коммерческой тайны</t>
+  </si>
+  <si>
+    <t>Технологический стек ограничен используемыми в Банке технологиями Java, .NET</t>
+  </si>
+  <si>
+    <t>Для очереди сообщений должна быть использована Kafka</t>
   </si>
 </sst>
 </file>
@@ -748,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="2" max="2" width="6.81640625" customWidth="1"/>
@@ -783,353 +783,345 @@
         <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="62">
       <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="7" spans="2:4" ht="62">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="62">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" ht="46.5">
-      <c r="B7" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="9" spans="2:4" ht="62">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="46.5">
-      <c r="B8" s="3" t="s">
+      <c r="C9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:4" ht="93">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+    </row>
+    <row r="11" spans="2:4" ht="46.5">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" ht="31">
-      <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="2:4" ht="46.5">
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="31">
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="C11" s="4" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D11" s="4"/>
     </row>
     <row r="12" spans="2:4" ht="62">
       <c r="B12" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="2:4" ht="31">
+    <row r="13" spans="2:4" ht="46.5">
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="2:4" ht="46.5">
       <c r="B14" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="2:4" ht="30" customHeight="1">
       <c r="B15" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D15" s="15"/>
     </row>
     <row r="16" spans="2:4" ht="59" customHeight="1">
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="B17" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="B19" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D19" s="15"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="B21" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1">
       <c r="B25" s="6" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:4" ht="31">
+    <row r="26" spans="1:4" ht="46.5">
       <c r="B26" s="7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="46.5">
+      <c r="B27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="31">
-      <c r="B27" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D28" s="13"/>
     </row>
-    <row r="29" spans="1:4" ht="46.5">
+    <row r="29" spans="1:4" ht="93">
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="62">
       <c r="B30" s="3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="B31" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D31" s="11"/>
     </row>
     <row r="32" spans="1:4" ht="35.25" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="63" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="35.25" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="35.25" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="64" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4" ht="35.25" customHeight="1">
-      <c r="A36" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="46.5">
       <c r="B36" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="31">
       <c r="B37" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="31">
-      <c r="B38" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="4"/>
+      <c r="D37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
